--- a/data/trans_orig/hab_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/hab_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2007</t>
+          <t>Nivel de hábitat en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197058</t>
+          <t>194759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>246501</t>
+          <t>248408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308125</t>
+          <t>305027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>372258</t>
+          <t>371689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>517706</t>
+          <t>516197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>598242</t>
+          <t>601197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160410</t>
+          <t>156925</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>207885</t>
+          <t>206416</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235182</t>
+          <t>234547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291238</t>
+          <t>291436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410355</t>
+          <t>405746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484020</t>
+          <t>481636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>318796</t>
+          <t>320321</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378078</t>
+          <t>378376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>362160</t>
+          <t>364580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>430346</t>
+          <t>431334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>703415</t>
+          <t>701818</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>794191</t>
+          <t>791155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>250245</t>
+          <t>248418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>306870</t>
+          <t>305314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>291327</t>
+          <t>290858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355604</t>
+          <t>351071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>561347</t>
+          <t>558806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>640579</t>
+          <t>641809</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>454394</t>
+          <t>458643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>530934</t>
+          <t>531044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>450309</t>
+          <t>448677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>521241</t>
+          <t>520988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,47 +1352,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>28,26%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>980912</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>930585</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>1035513</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>28,36%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>980912</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>928658</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1032978</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>327941</t>
+          <t>327014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397582</t>
+          <t>396422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>302620</t>
+          <t>304769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>367862</t>
+          <t>369041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>650621</t>
+          <t>647071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>742868</t>
+          <t>743052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450756</t>
+          <t>453088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>527386</t>
+          <t>523825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>419895</t>
+          <t>420081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493368</t>
+          <t>493141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895293</t>
+          <t>890180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001312</t>
+          <t>997213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316185</t>
+          <t>316749</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>380823</t>
+          <t>379709</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>281916</t>
+          <t>280587</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>343638</t>
+          <t>342258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>622025</t>
+          <t>613765</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>713485</t>
+          <t>711655</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202388</t>
+          <t>202829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>249298</t>
+          <t>248677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195141</t>
+          <t>193549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241163</t>
+          <t>237782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411738</t>
+          <t>411493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>473246</t>
+          <t>475430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115654</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160299</t>
+          <t>156991</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71381</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104760</t>
+          <t>106067</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>196376</t>
+          <t>195512</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>251998</t>
+          <t>252099</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103840</t>
+          <t>106963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145265</t>
+          <t>147450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>97494</t>
+          <t>98095</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135302</t>
+          <t>135660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>213174</t>
+          <t>214051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268991</t>
+          <t>271947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>53234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85268</t>
+          <t>83898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70320</t>
+          <t>70767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104249</t>
+          <t>102813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145803</t>
+          <t>146455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>891482</t>
+          <t>894327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>994954</t>
+          <t>992065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>986472</t>
+          <t>985633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1095733</t>
+          <t>1092946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1906489</t>
+          <t>1907354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2054953</t>
+          <t>2059726</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>632133</t>
+          <t>633206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>724258</t>
+          <t>727681</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>637222</t>
+          <t>637682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>729615</t>
+          <t>728465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1294800</t>
+          <t>1296600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1427229</t>
+          <t>1431455</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>906711</t>
+          <t>904658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1016408</t>
+          <t>1014251</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>919161</t>
+          <t>916996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1023060</t>
+          <t>1022651</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1857507</t>
+          <t>1859920</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2004766</t>
+          <t>2003939</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>646096</t>
+          <t>647647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>742228</t>
+          <t>744615</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>644580</t>
+          <t>644124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>740229</t>
+          <t>732873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1323580</t>
+          <t>1313239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1452440</t>
+          <t>1447598</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2012</t>
+          <t>Nivel de hábitat en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>171695</t>
+          <t>174885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223973</t>
+          <t>225286</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>322755</t>
+          <t>321527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>384120</t>
+          <t>385494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>510836</t>
+          <t>507503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>597839</t>
+          <t>593435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182149</t>
+          <t>182857</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236001</t>
+          <t>240078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249805</t>
+          <t>249684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309775</t>
+          <t>313342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>450079</t>
+          <t>446183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531122</t>
+          <t>529513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>286285</t>
+          <t>285483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>340823</t>
+          <t>346218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>372236</t>
+          <t>365831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>439030</t>
+          <t>435900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>674136</t>
+          <t>676452</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>766919</t>
+          <t>769198</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>226931</t>
+          <t>224388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282014</t>
+          <t>279634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270371</t>
+          <t>268636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>334406</t>
+          <t>332350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>509225</t>
+          <t>516588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>593876</t>
+          <t>596572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>515955</t>
+          <t>515657</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>598122</t>
+          <t>595189</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>465686</t>
+          <t>466875</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>541642</t>
+          <t>543629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1003712</t>
+          <t>1003187</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1118659</t>
+          <t>1116654</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>399516</t>
+          <t>405296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>482963</t>
+          <t>482795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>357615</t>
+          <t>357845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>425451</t>
+          <t>428867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>782906</t>
+          <t>785345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>882443</t>
+          <t>889150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539377</t>
+          <t>536779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626974</t>
+          <t>621855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>494566</t>
+          <t>490997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576461</t>
+          <t>570571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053417</t>
+          <t>1054388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1169856</t>
+          <t>1166368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>351654</t>
+          <t>353083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>425104</t>
+          <t>424328</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>297455</t>
+          <t>296371</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>365290</t>
+          <t>364971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>669052</t>
+          <t>671715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>763544</t>
+          <t>768370</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170831</t>
+          <t>170645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218413</t>
+          <t>213847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170776</t>
+          <t>171414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214343</t>
+          <t>213857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>351027</t>
+          <t>355321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416409</t>
+          <t>419109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87056</t>
+          <t>87307</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126777</t>
+          <t>126812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84800</t>
+          <t>84514</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124463</t>
+          <t>122975</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>184776</t>
+          <t>181123</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>239992</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101519</t>
+          <t>102147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142892</t>
+          <t>140964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>79430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116453</t>
+          <t>115674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192432</t>
+          <t>190979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244852</t>
+          <t>246248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>46579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78706</t>
+          <t>76824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50900</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>83443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107309</t>
+          <t>105906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151442</t>
+          <t>149108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>891767</t>
+          <t>894383</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>998518</t>
+          <t>1003928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>998529</t>
+          <t>996476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1107265</t>
+          <t>1106244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1916567</t>
+          <t>1916468</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2068340</t>
+          <t>2074462</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>701197</t>
+          <t>703835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>807025</t>
+          <t>813525</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>726419</t>
+          <t>725044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>828023</t>
+          <t>830379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1461288</t>
+          <t>1464169</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1605701</t>
+          <t>1609704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>962057</t>
+          <t>955338</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1078436</t>
+          <t>1070650</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>975377</t>
+          <t>977587</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1085635</t>
+          <t>1088421</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1976402</t>
+          <t>1969766</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2132006</t>
+          <t>2125919</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>655183</t>
+          <t>656144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>751625</t>
+          <t>753195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>651002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>749781</t>
+          <t>747301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5341,42 +5341,42 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1397714</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1329324</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1471797</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>21,1%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1397714</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1329243</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1464860</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2016</t>
+          <t>Nivel de hábitat en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121767</t>
+          <t>120346</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162523</t>
+          <t>160443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212194</t>
+          <t>211862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267119</t>
+          <t>269259</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345142</t>
+          <t>349720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>417407</t>
+          <t>420562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122188</t>
+          <t>120755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165809</t>
+          <t>163758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167535</t>
+          <t>166270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220052</t>
+          <t>219300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303957</t>
+          <t>302444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>371163</t>
+          <t>368874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226894</t>
+          <t>226603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>276928</t>
+          <t>277099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>286906</t>
+          <t>286335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>346972</t>
+          <t>347864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>532446</t>
+          <t>531915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>610356</t>
+          <t>611349</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195940</t>
+          <t>195621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243672</t>
+          <t>243495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220378</t>
+          <t>218959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>275992</t>
+          <t>273531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>429986</t>
+          <t>430499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>506859</t>
+          <t>502322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>502146</t>
+          <t>504525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>582739</t>
+          <t>584768</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>522063</t>
+          <t>523432</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>604216</t>
+          <t>605275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1046471</t>
+          <t>1040254</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1159166</t>
+          <t>1161378</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>477770</t>
+          <t>475705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>558812</t>
+          <t>555056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>451167</t>
+          <t>445487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>526847</t>
+          <t>522710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>948917</t>
+          <t>950618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1064256</t>
+          <t>1062608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>577351</t>
+          <t>581078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665769</t>
+          <t>667055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532707</t>
+          <t>532972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>613755</t>
+          <t>616424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,47 +6592,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>31,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1195596</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1136769</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1254835</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>29,41%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>30,87%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1195596</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1135429</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1252111</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>362976</t>
+          <t>361817</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>433754</t>
+          <t>434794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>333269</t>
+          <t>335483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>399767</t>
+          <t>405403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>712981</t>
+          <t>716529</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>813200</t>
+          <t>814011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>224854</t>
+          <t>226107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273191</t>
+          <t>273220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210473</t>
+          <t>214838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>260619</t>
+          <t>261139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>454434</t>
+          <t>451997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>524286</t>
+          <t>520341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82062</t>
+          <t>82620</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120915</t>
+          <t>119683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87992</t>
+          <t>84757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124565</t>
+          <t>123810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176787</t>
+          <t>177439</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>233462</t>
+          <t>231305</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117907</t>
+          <t>120748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161852</t>
+          <t>163868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130193</t>
+          <t>128425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170783</t>
+          <t>170680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>258902</t>
+          <t>256718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317688</t>
+          <t>322703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42583</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74692</t>
+          <t>73081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46321</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73451</t>
+          <t>73894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95234</t>
+          <t>95721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138413</t>
+          <t>136694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>879706</t>
+          <t>880034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>982887</t>
+          <t>979683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>986223</t>
+          <t>979923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094998</t>
+          <t>1093219</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1895091</t>
+          <t>1886480</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2048305</t>
+          <t>2042238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>707446</t>
+          <t>706319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>809632</t>
+          <t>809818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>732436</t>
+          <t>735377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>832896</t>
+          <t>834352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1473107</t>
+          <t>1476082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1610044</t>
+          <t>1616953</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>962526</t>
+          <t>961921</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1070394</t>
+          <t>1069012</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>985967</t>
+          <t>979887</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1095405</t>
+          <t>1097721</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1976185</t>
+          <t>1976775</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2130996</t>
+          <t>2139807</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>622199</t>
+          <t>628493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>720482</t>
+          <t>720375</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>621416</t>
+          <t>623996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>719827</t>
+          <t>717495</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1276641</t>
+          <t>1277982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1414012</t>
+          <t>1407665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de hábitat en 2023</t>
+          <t>Nivel de hábitat en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>94327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129276</t>
+          <t>128894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195453</t>
+          <t>195669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235711</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>299672</t>
+          <t>302181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354510</t>
+          <t>356051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62305</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91619</t>
+          <t>92782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117162</t>
+          <t>116603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150921</t>
+          <t>149437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187014</t>
+          <t>188003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232908</t>
+          <t>231806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149604</t>
+          <t>151786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191309</t>
+          <t>191205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198779</t>
+          <t>199511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236946</t>
+          <t>238302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>361721</t>
+          <t>360937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>415189</t>
+          <t>417233</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140010</t>
+          <t>139583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177534</t>
+          <t>178574</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173068</t>
+          <t>170599</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206257</t>
+          <t>208448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>322598</t>
+          <t>321870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373450</t>
+          <t>372080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>374259</t>
+          <t>372168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>621456</t>
+          <t>624824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>458330</t>
+          <t>459475</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>754821</t>
+          <t>748573</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934792</t>
+          <t>933880</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1326291</t>
+          <t>1321526</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>339358</t>
+          <t>327534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>573410</t>
+          <t>572344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>470882</t>
+          <t>471285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1069587</t>
+          <t>1049393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>939594</t>
+          <t>942359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1657640</t>
+          <t>1635173</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671005</t>
+          <t>666709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1307512</t>
+          <t>1316327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>432374</t>
+          <t>426298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659089</t>
+          <t>660426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1208532</t>
+          <t>1218751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1994219</t>
+          <t>2046778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>274874</t>
+          <t>275923</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>466995</t>
+          <t>463102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>296069</t>
+          <t>294780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>459448</t>
+          <t>459188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>627469</t>
+          <t>637149</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>894679</t>
+          <t>898430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244309</t>
+          <t>243576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297905</t>
+          <t>296866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244834</t>
+          <t>243301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>289075</t>
+          <t>288131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>503929</t>
+          <t>502783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>570377</t>
+          <t>574237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109342</t>
+          <t>110547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>154184</t>
+          <t>156245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>123153</t>
+          <t>124596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>163148</t>
+          <t>161746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>246561</t>
+          <t>249690</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>305087</t>
+          <t>306032</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143455</t>
+          <t>140382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195234</t>
+          <t>195791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143340</t>
+          <t>144731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182652</t>
+          <t>184088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>296132</t>
+          <t>299382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364347</t>
+          <t>362688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100732</t>
+          <t>99340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72971</t>
+          <t>72313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101603</t>
+          <t>101389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144808</t>
+          <t>143079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188187</t>
+          <t>189877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>712697</t>
+          <t>713451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1019005</t>
+          <t>1013309</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>905154</t>
+          <t>916184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1230295</t>
+          <t>1228865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1744326</t>
+          <t>1764580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2193415</t>
+          <t>2182849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>572701</t>
+          <t>557802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>779612</t>
+          <t>783756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>743240</t>
+          <t>742897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1447953</t>
+          <t>1450434</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1404917</t>
+          <t>1421824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2207991</t>
+          <t>2200080</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>998368</t>
+          <t>1003425</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1706520</t>
+          <t>1677969</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>770619</t>
+          <t>771565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1044363</t>
+          <t>1038464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1915326</t>
+          <t>1913565</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2747933</t>
+          <t>2733116</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>496799</t>
+          <t>488283</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>709036</t>
+          <t>700510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>555226</t>
+          <t>546123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>737123</t>
+          <t>737560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1129585</t>
+          <t>1143526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1417414</t>
+          <t>1420875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/hab_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/hab_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>194759</t>
+          <t>196914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248408</t>
+          <t>247728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>305027</t>
+          <t>305406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371689</t>
+          <t>371915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>516197</t>
+          <t>516518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>601197</t>
+          <t>600383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>156925</t>
+          <t>162167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206416</t>
+          <t>210610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234547</t>
+          <t>230772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291436</t>
+          <t>286543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405746</t>
+          <t>409119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481636</t>
+          <t>480682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320321</t>
+          <t>317041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378376</t>
+          <t>378899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>364580</t>
+          <t>364617</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>431334</t>
+          <t>434122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>701818</t>
+          <t>701887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>791155</t>
+          <t>793253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248418</t>
+          <t>250502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>308315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>290858</t>
+          <t>289493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>351071</t>
+          <t>350733</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>558806</t>
+          <t>559962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>641809</t>
+          <t>643553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>458643</t>
+          <t>459732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>531044</t>
+          <t>531026</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>448677</t>
+          <t>448459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>520988</t>
+          <t>523261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>930585</t>
+          <t>928322</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1035513</t>
+          <t>1033243</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>327014</t>
+          <t>329832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>396422</t>
+          <t>397583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>304769</t>
+          <t>304925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>369041</t>
+          <t>365174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>647071</t>
+          <t>640556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>743052</t>
+          <t>740618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453088</t>
+          <t>452924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523825</t>
+          <t>527368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,49 +1543,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>31,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>454879</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>419752</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>490992</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>26,44%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>30,93%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>454879</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>420081</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>493141</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>880</t>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>890180</t>
+          <t>891287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>997213</t>
+          <t>997270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316749</t>
+          <t>317612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>379709</t>
+          <t>382309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>280587</t>
+          <t>281037</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>342258</t>
+          <t>344167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>613765</t>
+          <t>614947</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>711655</t>
+          <t>709537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202829</t>
+          <t>202620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248677</t>
+          <t>251538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193549</t>
+          <t>195782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237782</t>
+          <t>239565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411493</t>
+          <t>409399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475430</t>
+          <t>473683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115466</t>
+          <t>112285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156991</t>
+          <t>155622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70098</t>
+          <t>72049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>106067</t>
+          <t>107197</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>195512</t>
+          <t>198574</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>252099</t>
+          <t>253371</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106963</t>
+          <t>104099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147450</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98095</t>
+          <t>96293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>133885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214051</t>
+          <t>216349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271947</t>
+          <t>271048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83898</t>
+          <t>83977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42300</t>
+          <t>42411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70767</t>
+          <t>70883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102813</t>
+          <t>101851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146455</t>
+          <t>144606</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>894327</t>
+          <t>892150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>992065</t>
+          <t>993383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>985633</t>
+          <t>976978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1092946</t>
+          <t>1092184</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1907354</t>
+          <t>1908290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2059726</t>
+          <t>2056034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>633206</t>
+          <t>628615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>727681</t>
+          <t>723875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>637682</t>
+          <t>642517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>728465</t>
+          <t>731585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1296600</t>
+          <t>1293942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1431455</t>
+          <t>1427372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>904658</t>
+          <t>912636</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1014251</t>
+          <t>1017984</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>916996</t>
+          <t>915841</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1022651</t>
+          <t>1022475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1859920</t>
+          <t>1857369</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2003939</t>
+          <t>2012713</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>647647</t>
+          <t>651405</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>744615</t>
+          <t>748549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>644124</t>
+          <t>642185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>732873</t>
+          <t>737355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1313239</t>
+          <t>1311725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1447598</t>
+          <t>1450793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174885</t>
+          <t>174946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225286</t>
+          <t>227148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321527</t>
+          <t>320398</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>385494</t>
+          <t>388809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507503</t>
+          <t>507839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>593435</t>
+          <t>592556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182857</t>
+          <t>182266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240078</t>
+          <t>237515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249684</t>
+          <t>253572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313342</t>
+          <t>311190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446183</t>
+          <t>451298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529513</t>
+          <t>532793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>285483</t>
+          <t>286284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>346218</t>
+          <t>345373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>365831</t>
+          <t>370321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435900</t>
+          <t>438127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676452</t>
+          <t>673886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>769198</t>
+          <t>765242</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224388</t>
+          <t>225588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279634</t>
+          <t>283756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268636</t>
+          <t>270370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>332350</t>
+          <t>331432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>516588</t>
+          <t>512292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596572</t>
+          <t>596662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>515657</t>
+          <t>511924</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>595189</t>
+          <t>594525</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>466875</t>
+          <t>467276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>543629</t>
+          <t>546309</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1003187</t>
+          <t>1003910</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1116654</t>
+          <t>1112592</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>405296</t>
+          <t>401866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>482795</t>
+          <t>478777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>357845</t>
+          <t>356606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>428867</t>
+          <t>428715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>785345</t>
+          <t>785691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>889150</t>
+          <t>889540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536779</t>
+          <t>540020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621855</t>
+          <t>623817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>490997</t>
+          <t>495696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570571</t>
+          <t>572540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054388</t>
+          <t>1053804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1166368</t>
+          <t>1170139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>353083</t>
+          <t>351531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>424328</t>
+          <t>422438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>296371</t>
+          <t>296302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>364971</t>
+          <t>363615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>671715</t>
+          <t>669818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>768370</t>
+          <t>773052</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170645</t>
+          <t>168142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213847</t>
+          <t>213932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171414</t>
+          <t>169829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213857</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355321</t>
+          <t>351699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419109</t>
+          <t>415537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>86614</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126812</t>
+          <t>129162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84514</t>
+          <t>84507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122975</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>181123</t>
+          <t>182051</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>239992</t>
+          <t>238850</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102147</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140964</t>
+          <t>142569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>79395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115674</t>
+          <t>118474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190979</t>
+          <t>191514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246248</t>
+          <t>247268</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46579</t>
+          <t>47463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76824</t>
+          <t>77382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83443</t>
+          <t>84748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105906</t>
+          <t>105660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149108</t>
+          <t>150905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>894383</t>
+          <t>892885</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1003928</t>
+          <t>998861</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>996476</t>
+          <t>995323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1106244</t>
+          <t>1110099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1916468</t>
+          <t>1918355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2074462</t>
+          <t>2073559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>703835</t>
+          <t>706267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>813525</t>
+          <t>810360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>725044</t>
+          <t>726599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>830379</t>
+          <t>830397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1464169</t>
+          <t>1460501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1609704</t>
+          <t>1604135</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>955338</t>
+          <t>960130</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1070650</t>
+          <t>1073777</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>977587</t>
+          <t>965914</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1088421</t>
+          <t>1087103</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1969766</t>
+          <t>1971426</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2125919</t>
+          <t>2128852</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>656144</t>
+          <t>656673</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>753195</t>
+          <t>746821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>651002</t>
+          <t>650883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>747301</t>
+          <t>750320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1329324</t>
+          <t>1327294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1471797</t>
+          <t>1461562</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120346</t>
+          <t>121708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160443</t>
+          <t>162384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211862</t>
+          <t>211766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269259</t>
+          <t>270357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>342218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>420562</t>
+          <t>413203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120755</t>
+          <t>121092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163758</t>
+          <t>164188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166270</t>
+          <t>168648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219300</t>
+          <t>218961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>302444</t>
+          <t>299717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>368874</t>
+          <t>369058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226603</t>
+          <t>223669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>277099</t>
+          <t>279418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>286335</t>
+          <t>285277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347864</t>
+          <t>350353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>531915</t>
+          <t>532140</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>611349</t>
+          <t>611383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195621</t>
+          <t>194892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243495</t>
+          <t>245367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>218959</t>
+          <t>219526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273531</t>
+          <t>277143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>430499</t>
+          <t>425083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>502322</t>
+          <t>502505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>504525</t>
+          <t>501170</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>584768</t>
+          <t>580490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>523432</t>
+          <t>524770</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>605275</t>
+          <t>604631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1040254</t>
+          <t>1046207</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1161378</t>
+          <t>1163014</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>475705</t>
+          <t>477705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>555056</t>
+          <t>556925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>445487</t>
+          <t>444997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>522710</t>
+          <t>527553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>950618</t>
+          <t>946881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1062608</t>
+          <t>1061332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581078</t>
+          <t>584716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667055</t>
+          <t>666914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532972</t>
+          <t>529734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616424</t>
+          <t>609302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1136769</t>
+          <t>1139835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1254835</t>
+          <t>1259653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>361817</t>
+          <t>358981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>434794</t>
+          <t>428764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335483</t>
+          <t>330829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>405403</t>
+          <t>402349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>716529</t>
+          <t>713766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>814011</t>
+          <t>815567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226107</t>
+          <t>226281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273220</t>
+          <t>275329</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214838</t>
+          <t>212327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261139</t>
+          <t>259625</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>449816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>520341</t>
+          <t>515285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82620</t>
+          <t>83202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119683</t>
+          <t>122942</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84757</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123810</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>177439</t>
+          <t>176292</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231305</t>
+          <t>231374</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120748</t>
+          <t>118039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163868</t>
+          <t>161740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128425</t>
+          <t>129896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170680</t>
+          <t>171260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>256718</t>
+          <t>259846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>322703</t>
+          <t>318630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73081</t>
+          <t>72414</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45603</t>
+          <t>46251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73894</t>
+          <t>73730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95721</t>
+          <t>97069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136694</t>
+          <t>136171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>880034</t>
+          <t>879221</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>979683</t>
+          <t>984371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>979923</t>
+          <t>983340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1093219</t>
+          <t>1096769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1886480</t>
+          <t>1893509</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2042238</t>
+          <t>2050613</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>706319</t>
+          <t>711029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>809818</t>
+          <t>806387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>735377</t>
+          <t>731535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>834352</t>
+          <t>835156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1476082</t>
+          <t>1465056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1616953</t>
+          <t>1613393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>961921</t>
+          <t>968546</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1069012</t>
+          <t>1073031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>979887</t>
+          <t>981110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1097721</t>
+          <t>1093165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1976775</t>
+          <t>1969659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2139807</t>
+          <t>2131657</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>628493</t>
+          <t>622188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>720375</t>
+          <t>719231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>623996</t>
+          <t>620838</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>717495</t>
+          <t>717759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1277982</t>
+          <t>1276005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1407665</t>
+          <t>1407757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>120081</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94327</t>
+          <t>102154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128894</t>
+          <t>138917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>214695</t>
+          <t>228333</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195669</t>
+          <t>205238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>247544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>326167</t>
+          <t>348414</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>302181</t>
+          <t>322065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>356051</t>
+          <t>377596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75833</t>
+          <t>94640</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61076</t>
+          <t>78381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92782</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>133353</t>
+          <t>146798</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116603</t>
+          <t>129986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149437</t>
+          <t>167815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>209187</t>
+          <t>241439</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188003</t>
+          <t>217593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231806</t>
+          <t>268950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>187008</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151786</t>
+          <t>164294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191205</t>
+          <t>210025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>218259</t>
+          <t>243045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>199511</t>
+          <t>223412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>238302</t>
+          <t>264003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>387572</t>
+          <t>430053</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360937</t>
+          <t>399081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>417233</t>
+          <t>459292</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>158320</t>
+          <t>176801</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139583</t>
+          <t>155449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>178574</t>
+          <t>199637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>189200</t>
+          <t>203861</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170599</t>
+          <t>183886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208448</t>
+          <t>221686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>347520</t>
+          <t>380662</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>321870</t>
+          <t>350293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372080</t>
+          <t>406972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>541161</t>
+          <t>579567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>372168</t>
+          <t>531332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>624824</t>
+          <t>625190</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>607474</t>
+          <t>600059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>459475</t>
+          <t>563150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>748573</t>
+          <t>641178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1148635</t>
+          <t>1179626</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>933880</t>
+          <t>1118692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1321526</t>
+          <t>1235412</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>495262</t>
+          <t>552259</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>327534</t>
+          <t>506021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>572344</t>
+          <t>604259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>654656</t>
+          <t>490592</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>471285</t>
+          <t>451175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1049393</t>
+          <t>525685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1149918</t>
+          <t>1042852</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>942359</t>
+          <t>984678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1635173</t>
+          <t>1106803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>857738</t>
+          <t>678130</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666709</t>
+          <t>628335</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1316327</t>
+          <t>734503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>576008</t>
+          <t>646393</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>426298</t>
+          <t>608060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660426</t>
+          <t>689779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1433746</t>
+          <t>1324523</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1218751</t>
+          <t>1262311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2046778</t>
+          <t>1391184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>396166</t>
+          <t>420610</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275923</t>
+          <t>376306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>463102</t>
+          <t>463325</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>399685</t>
+          <t>434348</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>294780</t>
+          <t>403440</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>459188</t>
+          <t>470407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>795851</t>
+          <t>854958</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>637149</t>
+          <t>799358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>898430</t>
+          <t>907582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>270031</t>
+          <t>285024</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243576</t>
+          <t>254943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296866</t>
+          <t>313522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>267803</t>
+          <t>287430</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243301</t>
+          <t>265087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288131</t>
+          <t>312659</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>537835</t>
+          <t>572454</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>502783</t>
+          <t>538494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>574237</t>
+          <t>613307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131241</t>
+          <t>151934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>110547</t>
+          <t>130378</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156245</t>
+          <t>176480</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>143169</t>
+          <t>172402</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124596</t>
+          <t>153145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161746</t>
+          <t>193981</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>274409</t>
+          <t>324337</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>249690</t>
+          <t>292657</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>306032</t>
+          <t>356910</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>165651</t>
+          <t>182588</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>157538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195791</t>
+          <t>208389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>163839</t>
+          <t>181400</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144731</t>
+          <t>161756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184088</t>
+          <t>202315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>329490</t>
+          <t>363988</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299382</t>
+          <t>331367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362688</t>
+          <t>400226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>92041</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>73547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99340</t>
+          <t>115119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85652</t>
+          <t>93644</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72313</t>
+          <t>79193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101389</t>
+          <t>109228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>165352</t>
+          <t>185685</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143079</t>
+          <t>161423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189877</t>
+          <t>210880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>922664</t>
+          <t>984672</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>713451</t>
+          <t>921429</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1013309</t>
+          <t>1044234</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1089973</t>
+          <t>1115822</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>916184</t>
+          <t>1067224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1228865</t>
+          <t>1165470</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012637</t>
+          <t>2100494</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1764580</t>
+          <t>2016393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2182849</t>
+          <t>2175800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>702336</t>
+          <t>798834</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>557802</t>
+          <t>744338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>783756</t>
+          <t>858821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>931178</t>
+          <t>809793</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>742897</t>
+          <t>765071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1450434</t>
+          <t>856802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1633514</t>
+          <t>1608627</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1421824</t>
+          <t>1540277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2200080</t>
+          <t>1677516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1192702</t>
+          <t>1047726</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1003425</t>
+          <t>987288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1677969</t>
+          <t>1116315</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>771565</t>
+          <t>1024122</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1038464</t>
+          <t>1121808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2150809</t>
+          <t>2118564</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1913565</t>
+          <t>2038963</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2733116</t>
+          <t>2196970</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>634187</t>
+          <t>689451</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488283</t>
+          <t>640417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>700510</t>
+          <t>751372</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>674537</t>
+          <t>731853</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>546123</t>
+          <t>690258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>737560</t>
+          <t>775188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1308723</t>
+          <t>1421305</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1143526</t>
+          <t>1355699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1420875</t>
+          <t>1485155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
